--- a/agrra_monitoring/data_raw/ATG_NEMMA_2025/Calculated/BenthicCover.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NEMMA_2025/Calculated/BenthicCover.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\ATG\Calculated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NEMMA&amp;CadesReef2025\Calculated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B5A154-54A9-4218-85C1-624CC4F6163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09458590-D2B1-4C5B-BDD1-9A25F17BA734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="22" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="23" r:id="rId1"/>
     <sheet name="Metadata" sheetId="1" r:id="rId2"/>
     <sheet name="Overall" sheetId="2" r:id="rId3"/>
     <sheet name="tAINV" sheetId="3" r:id="rId4"/>
@@ -36,7 +36,7 @@
     <sheet name="tPEY" sheetId="20" r:id="rId21"/>
     <sheet name="tTA" sheetId="21" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -4255,12 +4255,40 @@
     <t>TASstd</t>
   </si>
   <si>
-    <t>Created: 2025 May 29</t>
-  </si>
-  <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
+    <t>Created: 2026 May 29</t>
+  </si>
+  <si>
+    <t>AGRRA Terms of Data Service</t>
+  </si>
+  <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -4270,23 +4298,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Margaret Wilson. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -4295,7 +4307,330 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
 </t>
     </r>
     <r>
@@ -4307,7 +4642,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
+      <t>A. Guidance for Original Data Contributors</t>
     </r>
     <r>
       <rPr>
@@ -4316,7 +4651,167 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -4328,7 +4823,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
+      <t>B. Guidance for Third-Party Data Users</t>
     </r>
     <r>
       <rPr>
@@ -4337,8 +4832,8 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -4349,7 +4844,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
+      <t xml:space="preserve">How to cite original data contributors: </t>
     </r>
     <r>
       <rPr>
@@ -4357,9 +4852,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -4370,7 +4864,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
+      <t>How to acknowledge AGRRA:</t>
     </r>
     <r>
       <rPr>
@@ -4378,9 +4872,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -4391,7 +4884,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
     </r>
     <r>
       <rPr>
@@ -4399,8 +4892,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
     </r>
     <r>
       <rPr>
@@ -4411,7 +4904,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
+      <t>Direct contact and collaboration:</t>
     </r>
     <r>
       <rPr>
@@ -4419,11 +4912,30 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
 </t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -4433,7 +4945,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
+      <t>Data Integrity:</t>
     </r>
     <r>
       <rPr>
@@ -4441,19 +4953,9 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4463,7 +4965,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
+      <t>No Warranty:</t>
     </r>
     <r>
       <rPr>
@@ -4471,8 +4973,71 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
   <si>
     <r>
@@ -4496,23 +5061,30 @@
     </r>
   </si>
   <si>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>©</t>
+      <t>Format of Data:</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -4520,11 +5092,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4548,16 +5127,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4580,7 +5178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -4598,6 +5196,66 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -4607,7 +5265,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -4730,16 +5403,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4758,126 +5432,117 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{F7D7BDC0-2954-439B-8989-81F59B970C4B}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{9272200D-7629-43FC-A159-4D699ACF37E8}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{B47616B3-4D9B-44DA-B8EC-552335303F46}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -4890,61 +5555,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0812F13-33D1-455D-A16D-CE4385A664F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5233,1051 +5843,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A7943F-6750-452B-A14A-5D89088566E4}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D760D0B-B1C0-40D6-9154-0F3E6CDFDE40}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="14" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="14"/>
+    <col min="2" max="2" width="11.26953125" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>1404</v>
       </c>
       <c r="B1" s="13"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B2" s="13"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="15" t="s">
         <v>1405</v>
       </c>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="19"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="22"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="23" t="s">
         <v>1406</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="25"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
         <v>1407</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="18"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="28"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="31"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="31"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="31"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="31"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="31"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="31"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="31"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="31"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="31"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="31"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="31"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="31"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="31"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="31"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="31"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="31"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="31"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="31"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="31"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="31"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="31"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="31"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="31"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="30"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="30"/>
+      <c r="U41" s="30"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="14" t="s">
         <v>1408</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="31"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="31"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="31"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="31"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="31"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="31"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="29"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="31"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="31"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="S50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="31"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="29"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="31"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="31"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="29"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="31"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="29"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="31"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="31"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="29"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30"/>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="30"/>
+      <c r="S56" s="30"/>
+      <c r="T56" s="30"/>
+      <c r="U56" s="30"/>
+      <c r="V56" s="30"/>
+      <c r="W56" s="31"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="29"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="30"/>
+      <c r="S57" s="30"/>
+      <c r="T57" s="30"/>
+      <c r="U57" s="30"/>
+      <c r="V57" s="30"/>
+      <c r="W57" s="31"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="31"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="29"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
+      <c r="S59" s="30"/>
+      <c r="T59" s="30"/>
+      <c r="U59" s="30"/>
+      <c r="V59" s="30"/>
+      <c r="W59" s="31"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="29"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="31"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="31"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="29"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="30"/>
+      <c r="O62" s="30"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="30"/>
+      <c r="R62" s="30"/>
+      <c r="S62" s="30"/>
+      <c r="T62" s="30"/>
+      <c r="U62" s="30"/>
+      <c r="V62" s="30"/>
+      <c r="W62" s="31"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
+      <c r="W63" s="34"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="35"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="36" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="37"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="37"/>
+      <c r="S65" s="37"/>
+      <c r="T65" s="37"/>
+      <c r="U65" s="37"/>
+      <c r="V65" s="37"/>
+      <c r="W65" s="38"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="39"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="40"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="40"/>
+      <c r="P66" s="40"/>
+      <c r="Q66" s="40"/>
+      <c r="R66" s="40"/>
+      <c r="S66" s="40"/>
+      <c r="T66" s="40"/>
+      <c r="U66" s="40"/>
+      <c r="V66" s="40"/>
+      <c r="W66" s="41"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="42" t="s">
         <v>1409</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="24"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="30"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="30"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="30"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="30"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="30"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="30"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="30"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="30"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="30"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="30"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="30"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="30"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="30"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="30"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="30"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="30"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="30"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="30"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="30"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="30"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="30"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-      <c r="W39" s="30"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="30"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-      <c r="W41" s="30"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="30"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="30"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-      <c r="W44" s="30"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
-      <c r="W45" s="30"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="30"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="36"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="37" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="38"/>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="38"/>
-      <c r="Q48" s="38"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="38"/>
-      <c r="T48" s="38"/>
-      <c r="U48" s="38"/>
-      <c r="V48" s="38"/>
-      <c r="W48" s="39"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="42"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="43" t="s">
-        <v>1411</v>
-      </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="44"/>
-      <c r="N50" s="44"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="44"/>
-      <c r="V50" s="44"/>
-      <c r="W50" s="45"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="46" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="48"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="48"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="48"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="48"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="48"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="48"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="48"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="48"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="48"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="48"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="48"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="48"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="48"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="48"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="48"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="48"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="48"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="43"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="43"/>
+      <c r="R67" s="43"/>
+      <c r="S67" s="43"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="43"/>
+      <c r="V67" s="43"/>
+      <c r="W67" s="44"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="35"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="35"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:ID10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -6287,7 +7447,7 @@
     <col min="8" max="238" width="12" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -7003,7 +8163,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="2" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -7233,31 +8393,31 @@
         <v>0</v>
       </c>
       <c r="BY2" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BZ2" s="8">
         <v>0</v>
       </c>
       <c r="CA2" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CB2" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="CC2" s="8">
         <v>0</v>
       </c>
       <c r="CD2" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CE2" s="8">
-        <v>6.6666700000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="CF2" s="8">
         <v>0</v>
       </c>
       <c r="CG2" s="8">
-        <v>1.105542E-2</v>
+        <v>0</v>
       </c>
       <c r="CH2" s="8">
         <v>0</v>
@@ -7269,13 +8429,13 @@
         <v>0</v>
       </c>
       <c r="CK2" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CL2" s="8">
         <v>0</v>
       </c>
       <c r="CM2" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="CN2" s="8">
         <v>0</v>
@@ -7332,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="DF2" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="DG2" s="8">
         <v>0</v>
       </c>
       <c r="DH2" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="DI2" s="8">
         <v>0</v>
@@ -7719,7 +8879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -7769,13 +8929,13 @@
         <v>0</v>
       </c>
       <c r="Q3" s="8">
-        <v>2.833333E-2</v>
+        <v>1.6666700000000001E-3</v>
       </c>
       <c r="R3" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="S3" s="8">
-        <v>5.0470010000000003E-2</v>
+        <v>3.7267799999999998E-3</v>
       </c>
       <c r="T3" s="8">
         <v>0</v>
@@ -7958,13 +9118,13 @@
         <v>0</v>
       </c>
       <c r="CB3" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="CC3" s="8">
         <v>0</v>
       </c>
       <c r="CD3" s="8">
-        <v>1.118034E-2</v>
+        <v>0</v>
       </c>
       <c r="CE3" s="8">
         <v>0</v>
@@ -7985,13 +9145,13 @@
         <v>0</v>
       </c>
       <c r="CK3" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CL3" s="8">
         <v>0</v>
       </c>
       <c r="CM3" s="8">
-        <v>4.71405E-3</v>
+        <v>0</v>
       </c>
       <c r="CN3" s="8">
         <v>0</v>
@@ -8021,13 +9181,13 @@
         <v>0</v>
       </c>
       <c r="CW3" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CX3" s="8">
         <v>0</v>
       </c>
       <c r="CY3" s="8">
-        <v>4.71405E-3</v>
+        <v>0</v>
       </c>
       <c r="CZ3" s="8">
         <v>0</v>
@@ -8183,13 +9343,13 @@
         <v>0</v>
       </c>
       <c r="EY3" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ3" s="8">
         <v>0</v>
       </c>
       <c r="FA3" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="FB3" s="8">
         <v>0</v>
@@ -8336,13 +9496,13 @@
         <v>0</v>
       </c>
       <c r="GX3" s="8">
-        <v>6.6666700000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="GY3" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="GZ3" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="HA3" s="8">
         <v>0</v>
@@ -8435,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -8782,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="DL4" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="DM4" s="8">
         <v>0</v>
       </c>
       <c r="DN4" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="DO4" s="8">
         <v>0</v>
@@ -8899,13 +10059,13 @@
         <v>0</v>
       </c>
       <c r="EY4" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ4" s="8">
         <v>0</v>
       </c>
       <c r="FA4" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="FB4" s="8">
         <v>0</v>
@@ -9052,13 +10212,13 @@
         <v>0</v>
       </c>
       <c r="GX4" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="GY4" s="8">
         <v>0</v>
       </c>
       <c r="GZ4" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="HA4" s="8">
         <v>0</v>
@@ -9097,13 +10257,13 @@
         <v>0</v>
       </c>
       <c r="HM4" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HN4" s="8">
         <v>0</v>
       </c>
       <c r="HO4" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HP4" s="8">
         <v>0</v>
@@ -9115,13 +10275,13 @@
         <v>0</v>
       </c>
       <c r="HS4" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HT4" s="8">
         <v>0</v>
       </c>
       <c r="HU4" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HV4" s="8">
         <v>0</v>
@@ -9151,7 +10311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -9282,13 +10442,13 @@
         <v>0</v>
       </c>
       <c r="AR5" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="AS5" s="8">
         <v>0</v>
       </c>
       <c r="AT5" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="AU5" s="8">
         <v>0</v>
@@ -9390,22 +10550,22 @@
         <v>0</v>
       </c>
       <c r="CB5" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="CC5" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="CD5" s="8">
-        <v>2.813657E-2</v>
+        <v>0</v>
       </c>
       <c r="CE5" s="8">
-        <v>6.6666700000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="CF5" s="8">
         <v>0</v>
       </c>
       <c r="CG5" s="8">
-        <v>9.4280900000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="CH5" s="8">
         <v>0</v>
@@ -9615,13 +10775,13 @@
         <v>0</v>
       </c>
       <c r="EY5" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ5" s="8">
         <v>0</v>
       </c>
       <c r="FA5" s="8">
-        <v>1.118034E-2</v>
+        <v>0</v>
       </c>
       <c r="FB5" s="8">
         <v>0</v>
@@ -9768,13 +10928,13 @@
         <v>0</v>
       </c>
       <c r="GX5" s="8">
-        <v>2.1666669999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="GY5" s="8">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="GZ5" s="8">
-        <v>1.5723299999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="HA5" s="8">
         <v>0</v>
@@ -9840,13 +11000,13 @@
         <v>0</v>
       </c>
       <c r="HV5" s="8">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="HW5" s="8">
         <v>0</v>
       </c>
       <c r="HX5" s="8">
-        <v>1.5275250000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="HY5" s="8">
         <v>0</v>
@@ -9867,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -10097,31 +11257,31 @@
         <v>0</v>
       </c>
       <c r="BY6" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BZ6" s="8">
         <v>0</v>
       </c>
       <c r="CA6" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CB6" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="CC6" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="CD6" s="8">
-        <v>1.802776E-2</v>
+        <v>0</v>
       </c>
       <c r="CE6" s="8">
-        <v>8.3333299999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="CF6" s="8">
         <v>0</v>
       </c>
       <c r="CG6" s="8">
-        <v>1.213352E-2</v>
+        <v>0</v>
       </c>
       <c r="CH6" s="8">
         <v>0</v>
@@ -10196,13 +11356,13 @@
         <v>0</v>
       </c>
       <c r="DF6" s="8">
-        <v>1.1666670000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="DG6" s="8">
         <v>0</v>
       </c>
       <c r="DH6" s="8">
-        <v>2.608746E-2</v>
+        <v>0</v>
       </c>
       <c r="DI6" s="8">
         <v>0</v>
@@ -10484,13 +11644,13 @@
         <v>0</v>
       </c>
       <c r="GX6" s="8">
-        <v>7.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="GY6" s="8">
         <v>0</v>
       </c>
       <c r="GZ6" s="8">
-        <v>1.145644E-2</v>
+        <v>0</v>
       </c>
       <c r="HA6" s="8">
         <v>0</v>
@@ -10583,7 +11743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -10813,13 +11973,13 @@
         <v>0</v>
       </c>
       <c r="BY7" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="BZ7" s="8">
         <v>0</v>
       </c>
       <c r="CA7" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="CB7" s="8">
         <v>0</v>
@@ -10849,13 +12009,13 @@
         <v>0</v>
       </c>
       <c r="CK7" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="CL7" s="8">
         <v>0</v>
       </c>
       <c r="CM7" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="CN7" s="8">
         <v>0</v>
@@ -11047,13 +12207,13 @@
         <v>0</v>
       </c>
       <c r="EY7" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ7" s="8">
         <v>0</v>
       </c>
       <c r="FA7" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="FB7" s="8">
         <v>0</v>
@@ -11200,13 +12360,13 @@
         <v>0</v>
       </c>
       <c r="GX7" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="GY7" s="8">
         <v>0</v>
       </c>
       <c r="GZ7" s="8">
-        <v>7.6376300000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="HA7" s="8">
         <v>0</v>
@@ -11236,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="HJ7" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HK7" s="8">
         <v>0</v>
       </c>
       <c r="HL7" s="8">
-        <v>4.71405E-3</v>
+        <v>0</v>
       </c>
       <c r="HM7" s="8">
         <v>0</v>
@@ -11263,22 +12423,22 @@
         <v>0</v>
       </c>
       <c r="HS7" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HT7" s="8">
         <v>0</v>
       </c>
       <c r="HU7" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HV7" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HW7" s="8">
         <v>0</v>
       </c>
       <c r="HX7" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HY7" s="8">
         <v>0</v>
@@ -11299,7 +12459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -11367,13 +12527,13 @@
         <v>0</v>
       </c>
       <c r="W8" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="X8" s="8">
         <v>0</v>
       </c>
       <c r="Y8" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="8">
         <v>0</v>
@@ -11538,22 +12698,22 @@
         <v>0</v>
       </c>
       <c r="CB8" s="8">
-        <v>1.3333329999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="CC8" s="8">
         <v>0</v>
       </c>
       <c r="CD8" s="8">
-        <v>1.9720270000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="CE8" s="8">
-        <v>1.6666670000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="CF8" s="8">
         <v>0</v>
       </c>
       <c r="CG8" s="8">
-        <v>3.7267799999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="CH8" s="8">
         <v>0</v>
@@ -11619,13 +12779,13 @@
         <v>0</v>
       </c>
       <c r="DC8" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="DD8" s="8">
         <v>0</v>
       </c>
       <c r="DE8" s="8">
-        <v>1.118034E-2</v>
+        <v>0</v>
       </c>
       <c r="DF8" s="8">
         <v>0</v>
@@ -11763,13 +12923,13 @@
         <v>0</v>
       </c>
       <c r="EY8" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ8" s="8">
         <v>0</v>
       </c>
       <c r="FA8" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="FB8" s="8">
         <v>0</v>
@@ -11916,13 +13076,13 @@
         <v>0</v>
       </c>
       <c r="GX8" s="8">
-        <v>2.4166670000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="GY8" s="8">
-        <v>1.2500000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="GZ8" s="8">
-        <v>3.1147049999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="HA8" s="8">
         <v>0</v>
@@ -11979,22 +13139,22 @@
         <v>0</v>
       </c>
       <c r="HS8" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HT8" s="8">
         <v>0</v>
       </c>
       <c r="HU8" s="8">
-        <v>1.118034E-2</v>
+        <v>0</v>
       </c>
       <c r="HV8" s="8">
-        <v>1.3333329999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="HW8" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="HX8" s="8">
-        <v>1.7950549999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="HY8" s="8">
         <v>0</v>
@@ -12015,7 +13175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -12164,13 +13324,13 @@
         <v>0</v>
       </c>
       <c r="AX9" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="AY9" s="8">
         <v>0</v>
       </c>
       <c r="AZ9" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="BA9" s="8">
         <v>0</v>
@@ -12632,13 +13792,13 @@
         <v>0</v>
       </c>
       <c r="GX9" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="GY9" s="8">
         <v>0</v>
       </c>
       <c r="GZ9" s="8">
-        <v>7.4535599999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="HA9" s="8">
         <v>0</v>
@@ -12668,13 +13828,13 @@
         <v>0</v>
       </c>
       <c r="HJ9" s="8">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="HK9" s="8">
         <v>0</v>
       </c>
       <c r="HL9" s="8">
-        <v>2.2360680000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="HM9" s="8">
         <v>0</v>
@@ -12695,13 +13855,13 @@
         <v>0</v>
       </c>
       <c r="HS9" s="8">
-        <v>3.3333299999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="HT9" s="8">
         <v>0</v>
       </c>
       <c r="HU9" s="8">
-        <v>4.71405E-3</v>
+        <v>0</v>
       </c>
       <c r="HV9" s="8">
         <v>0</v>
@@ -12731,7 +13891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -12970,13 +14130,13 @@
         <v>0</v>
       </c>
       <c r="CB10" s="8">
-        <v>1.1666670000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="CC10" s="8">
         <v>0</v>
       </c>
       <c r="CD10" s="8">
-        <v>1.8633899999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="CE10" s="8">
         <v>0</v>
@@ -12997,13 +14157,13 @@
         <v>0</v>
       </c>
       <c r="CK10" s="8">
-        <v>1.3333329999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="CL10" s="8">
         <v>0</v>
       </c>
       <c r="CM10" s="8">
-        <v>2.2110830000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="CN10" s="8">
         <v>0</v>
@@ -13195,13 +14355,13 @@
         <v>0</v>
       </c>
       <c r="EY10" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="EZ10" s="8">
         <v>0</v>
       </c>
       <c r="FA10" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="FB10" s="8">
         <v>0</v>
@@ -13348,13 +14508,13 @@
         <v>0</v>
       </c>
       <c r="GX10" s="8">
-        <v>1.1666670000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="GY10" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="GZ10" s="8">
-        <v>8.9752700000000005E-3</v>
+        <v>0</v>
       </c>
       <c r="HA10" s="8">
         <v>0</v>
@@ -13456,7 +14616,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -13466,7 +14626,7 @@
     <col min="8" max="13" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -13507,7 +14667,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -13548,7 +14708,7 @@
         <v>3.7267799999999998E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -13589,7 +14749,7 @@
         <v>7.3124699999999997E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -13630,7 +14790,7 @@
         <v>1.8633899999999999E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -13671,7 +14831,7 @@
         <v>3.6400549999999997E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -13712,7 +14872,7 @@
         <v>4.4907309999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -13753,7 +14913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -13794,7 +14954,7 @@
         <v>2.8099530000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -13835,7 +14995,7 @@
         <v>3.7267799999999998E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -13885,7 +15045,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -13894,7 +15054,7 @@
     <col min="5" max="7" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -13917,7 +15077,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -13940,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -13963,7 +15123,7 @@
         <v>3.7267799999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -13986,7 +15146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -14009,7 +15169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -14032,7 +15192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -14055,7 +15215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -14078,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -14101,7 +15261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -14133,7 +15293,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:CM10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -14144,7 +15304,7 @@
     <col min="44" max="91" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -14419,7 +15579,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -14694,7 +15854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -14969,7 +16129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -15244,7 +16404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -15519,7 +16679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -15794,7 +16954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -16069,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -16344,7 +17504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -16619,7 +17779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -16903,7 +18063,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:CM10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -16915,7 +18075,7 @@
     <col min="44" max="91" width="12" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17190,7 +18350,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -17465,7 +18625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -17740,7 +18900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -18015,7 +19175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -18290,7 +19450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -18565,7 +19725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -18840,7 +20000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -19115,7 +20275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -19390,7 +20550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -19674,7 +20834,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:V10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -19685,7 +20845,7 @@
     <col min="11" max="22" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -19753,7 +20913,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -19821,7 +20981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -19889,7 +21049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -19957,7 +21117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -20025,7 +21185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -20093,7 +21253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -20161,7 +21321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -20229,7 +21389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -20297,7 +21457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -20374,7 +21534,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -20383,7 +21543,7 @@
     <col min="5" max="7" width="6" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -20406,7 +21566,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -20429,7 +21589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -20452,7 +21612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -20475,7 +21635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -20498,7 +21658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -20521,7 +21681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -20544,7 +21704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -20567,7 +21727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -20590,7 +21750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -20622,7 +21782,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -20631,7 +21791,7 @@
     <col min="5" max="7" width="10" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -20654,7 +21814,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -20677,7 +21837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -20700,7 +21860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -20723,7 +21883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -20746,7 +21906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -20769,7 +21929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -20792,7 +21952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -20815,7 +21975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -20838,7 +21998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -20870,7 +22030,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -20885,7 +22045,7 @@
     <col min="32" max="34" width="8" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -20989,7 +22149,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -21093,7 +22253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -21197,7 +22357,7 @@
         <v>3.7267799999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -21301,7 +22461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -21405,7 +22565,7 @@
         <v>1.4907119999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -21509,7 +22669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -21613,7 +22773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -21717,7 +22877,7 @@
         <v>3.7267799999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -21821,7 +22981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -21934,7 +23094,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -21945,7 +23105,7 @@
     <col min="14" max="19" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -22004,7 +23164,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -22063,7 +23223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -22122,7 +23282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -22181,7 +23341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -22240,7 +23400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -22299,7 +23459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -22358,7 +23518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -22417,7 +23577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -22476,7 +23636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -22544,14 +23704,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C216"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -22561,8 +23721,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -22572,8 +23732,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -22581,8 +23741,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
@@ -22590,8 +23750,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -22599,8 +23759,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -22608,8 +23768,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -22617,8 +23777,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
@@ -22626,8 +23786,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
@@ -22635,8 +23795,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
@@ -22644,8 +23804,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -22653,8 +23813,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -22662,8 +23822,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -22671,8 +23831,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -22680,8 +23840,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -22689,8 +23849,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="12"/>
       <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
@@ -22698,20 +23858,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -22721,8 +23881,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
@@ -22730,8 +23890,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
@@ -22739,8 +23899,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -22750,8 +23910,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
@@ -22759,8 +23919,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
       <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
@@ -22768,8 +23928,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
@@ -22777,8 +23937,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="11"/>
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
@@ -22786,8 +23946,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
       <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
@@ -22795,8 +23955,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="11"/>
       <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
@@ -22804,8 +23964,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="11"/>
       <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
@@ -22813,8 +23973,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="11"/>
       <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
@@ -22822,8 +23982,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="11"/>
       <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
@@ -22831,8 +23991,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
       <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
@@ -22840,8 +24000,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
       <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
@@ -22849,8 +24009,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
       <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
@@ -22858,8 +24018,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="11"/>
       <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
@@ -22867,8 +24027,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="11"/>
       <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
@@ -22876,8 +24036,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="11"/>
       <c r="B37" s="3" t="s">
         <v>73</v>
       </c>
@@ -22885,8 +24045,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="11"/>
       <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
@@ -22894,8 +24054,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="11"/>
       <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
@@ -22903,8 +24063,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="12"/>
       <c r="B40" s="5" t="s">
         <v>79</v>
       </c>
@@ -22912,8 +24072,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -22923,8 +24083,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="11"/>
       <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
@@ -22932,8 +24092,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="11"/>
       <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
@@ -22941,8 +24101,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="11"/>
       <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
@@ -22950,8 +24110,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="11"/>
       <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
@@ -22959,8 +24119,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="11"/>
       <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
@@ -22968,8 +24128,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="11"/>
       <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
@@ -22977,8 +24137,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="11"/>
       <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
@@ -22986,8 +24146,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="11"/>
       <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
@@ -22995,8 +24155,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="11"/>
       <c r="B50" s="3" t="s">
         <v>100</v>
       </c>
@@ -23004,8 +24164,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="11"/>
       <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
@@ -23013,8 +24173,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="11"/>
       <c r="B52" s="3" t="s">
         <v>104</v>
       </c>
@@ -23022,8 +24182,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="11"/>
       <c r="B53" s="3" t="s">
         <v>106</v>
       </c>
@@ -23031,8 +24191,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="11"/>
       <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
@@ -23040,8 +24200,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="12"/>
       <c r="B55" s="5" t="s">
         <v>110</v>
       </c>
@@ -23049,8 +24209,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B56" s="5" t="s">
@@ -23060,8 +24220,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
@@ -23071,8 +24231,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -23082,8 +24242,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="11"/>
       <c r="B59" s="3" t="s">
         <v>119</v>
       </c>
@@ -23091,8 +24251,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="11"/>
       <c r="B60" s="3" t="s">
         <v>121</v>
       </c>
@@ -23100,8 +24260,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="11"/>
       <c r="B61" s="3" t="s">
         <v>123</v>
       </c>
@@ -23109,8 +24269,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10"/>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="11"/>
       <c r="B62" s="3" t="s">
         <v>125</v>
       </c>
@@ -23118,8 +24278,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10"/>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="11"/>
       <c r="B63" s="3" t="s">
         <v>127</v>
       </c>
@@ -23127,8 +24287,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="11"/>
       <c r="B64" s="3" t="s">
         <v>129</v>
       </c>
@@ -23136,8 +24296,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="10"/>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="11"/>
       <c r="B65" s="3" t="s">
         <v>131</v>
       </c>
@@ -23145,8 +24305,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10"/>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="11"/>
       <c r="B66" s="3" t="s">
         <v>133</v>
       </c>
@@ -23154,8 +24314,8 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="10"/>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="11"/>
       <c r="B67" s="3" t="s">
         <v>135</v>
       </c>
@@ -23163,8 +24323,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="10"/>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="11"/>
       <c r="B68" s="3" t="s">
         <v>137</v>
       </c>
@@ -23172,8 +24332,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="12"/>
       <c r="B69" s="5" t="s">
         <v>139</v>
       </c>
@@ -23181,8 +24341,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B70" s="5" t="s">
@@ -23192,8 +24352,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="11" t="s">
         <v>143</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -23203,8 +24363,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="10"/>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="11"/>
       <c r="B72" s="3" t="s">
         <v>146</v>
       </c>
@@ -23212,8 +24372,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="10"/>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="11"/>
       <c r="B73" s="3" t="s">
         <v>148</v>
       </c>
@@ -23221,8 +24381,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="10"/>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="11"/>
       <c r="B74" s="3" t="s">
         <v>150</v>
       </c>
@@ -23230,8 +24390,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="10"/>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="11"/>
       <c r="B75" s="3" t="s">
         <v>152</v>
       </c>
@@ -23239,8 +24399,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="10"/>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="11"/>
       <c r="B76" s="3" t="s">
         <v>154</v>
       </c>
@@ -23248,8 +24408,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="10"/>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="11"/>
       <c r="B77" s="3" t="s">
         <v>156</v>
       </c>
@@ -23257,8 +24417,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="10"/>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="11"/>
       <c r="B78" s="3" t="s">
         <v>158</v>
       </c>
@@ -23266,8 +24426,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="10"/>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="11"/>
       <c r="B79" s="3" t="s">
         <v>160</v>
       </c>
@@ -23275,8 +24435,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="10"/>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="11"/>
       <c r="B80" s="3" t="s">
         <v>162</v>
       </c>
@@ -23284,8 +24444,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="10"/>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="11"/>
       <c r="B81" s="3" t="s">
         <v>164</v>
       </c>
@@ -23293,8 +24453,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="10"/>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="11"/>
       <c r="B82" s="3" t="s">
         <v>166</v>
       </c>
@@ -23302,8 +24462,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="10"/>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="11"/>
       <c r="B83" s="3" t="s">
         <v>168</v>
       </c>
@@ -23311,8 +24471,8 @@
         <v>169</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="10"/>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="11"/>
       <c r="B84" s="3" t="s">
         <v>170</v>
       </c>
@@ -23320,8 +24480,8 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="10"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="11"/>
       <c r="B85" s="3" t="s">
         <v>172</v>
       </c>
@@ -23329,8 +24489,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="10"/>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="11"/>
       <c r="B86" s="3" t="s">
         <v>174</v>
       </c>
@@ -23338,8 +24498,8 @@
         <v>175</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="10"/>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="11"/>
       <c r="B87" s="3" t="s">
         <v>176</v>
       </c>
@@ -23347,8 +24507,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="10"/>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="11"/>
       <c r="B88" s="3" t="s">
         <v>178</v>
       </c>
@@ -23356,8 +24516,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="10"/>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="11"/>
       <c r="B89" s="3" t="s">
         <v>180</v>
       </c>
@@ -23365,8 +24525,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="10"/>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="11"/>
       <c r="B90" s="3" t="s">
         <v>182</v>
       </c>
@@ -23374,8 +24534,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="10"/>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="11"/>
       <c r="B91" s="3" t="s">
         <v>184</v>
       </c>
@@ -23383,8 +24543,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="10"/>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="11"/>
       <c r="B92" s="3" t="s">
         <v>186</v>
       </c>
@@ -23392,8 +24552,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="10"/>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="11"/>
       <c r="B93" s="3" t="s">
         <v>188</v>
       </c>
@@ -23401,8 +24561,8 @@
         <v>189</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="10"/>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="11"/>
       <c r="B94" s="3" t="s">
         <v>190</v>
       </c>
@@ -23410,8 +24570,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="10"/>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="11"/>
       <c r="B95" s="3" t="s">
         <v>192</v>
       </c>
@@ -23419,8 +24579,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="10"/>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="11"/>
       <c r="B96" s="3" t="s">
         <v>194</v>
       </c>
@@ -23428,8 +24588,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="10"/>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="11"/>
       <c r="B97" s="3" t="s">
         <v>196</v>
       </c>
@@ -23437,8 +24597,8 @@
         <v>197</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="10"/>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="11"/>
       <c r="B98" s="3" t="s">
         <v>198</v>
       </c>
@@ -23446,8 +24606,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="10"/>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="11"/>
       <c r="B99" s="3" t="s">
         <v>200</v>
       </c>
@@ -23455,8 +24615,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="11"/>
       <c r="B100" s="3" t="s">
         <v>202</v>
       </c>
@@ -23464,8 +24624,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="10"/>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="11"/>
       <c r="B101" s="3" t="s">
         <v>204</v>
       </c>
@@ -23473,8 +24633,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="10"/>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="11"/>
       <c r="B102" s="3" t="s">
         <v>206</v>
       </c>
@@ -23482,8 +24642,8 @@
         <v>207</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="10"/>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="11"/>
       <c r="B103" s="3" t="s">
         <v>208</v>
       </c>
@@ -23491,8 +24651,8 @@
         <v>209</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="10"/>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="11"/>
       <c r="B104" s="3" t="s">
         <v>210</v>
       </c>
@@ -23500,8 +24660,8 @@
         <v>211</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="10"/>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="11"/>
       <c r="B105" s="3" t="s">
         <v>212</v>
       </c>
@@ -23509,8 +24669,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="10"/>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="11"/>
       <c r="B106" s="3" t="s">
         <v>214</v>
       </c>
@@ -23518,8 +24678,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="10"/>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="11"/>
       <c r="B107" s="3" t="s">
         <v>216</v>
       </c>
@@ -23527,8 +24687,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="10"/>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="11"/>
       <c r="B108" s="3" t="s">
         <v>218</v>
       </c>
@@ -23536,8 +24696,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="10"/>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="11"/>
       <c r="B109" s="3" t="s">
         <v>220</v>
       </c>
@@ -23545,8 +24705,8 @@
         <v>221</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="10"/>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="11"/>
       <c r="B110" s="3" t="s">
         <v>222</v>
       </c>
@@ -23554,8 +24714,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="10"/>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="11"/>
       <c r="B111" s="3" t="s">
         <v>224</v>
       </c>
@@ -23563,8 +24723,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="10"/>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="11"/>
       <c r="B112" s="3" t="s">
         <v>226</v>
       </c>
@@ -23572,8 +24732,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="10"/>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="11"/>
       <c r="B113" s="3" t="s">
         <v>228</v>
       </c>
@@ -23581,8 +24741,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="10"/>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="11"/>
       <c r="B114" s="3" t="s">
         <v>230</v>
       </c>
@@ -23590,8 +24750,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="10"/>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="11"/>
       <c r="B115" s="3" t="s">
         <v>232</v>
       </c>
@@ -23599,8 +24759,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="10"/>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="11"/>
       <c r="B116" s="3" t="s">
         <v>234</v>
       </c>
@@ -23608,8 +24768,8 @@
         <v>235</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="10"/>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="11"/>
       <c r="B117" s="3" t="s">
         <v>236</v>
       </c>
@@ -23617,8 +24777,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="10"/>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="11"/>
       <c r="B118" s="3" t="s">
         <v>238</v>
       </c>
@@ -23626,8 +24786,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="10"/>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="11"/>
       <c r="B119" s="3" t="s">
         <v>240</v>
       </c>
@@ -23635,8 +24795,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="10"/>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="11"/>
       <c r="B120" s="3" t="s">
         <v>242</v>
       </c>
@@ -23644,8 +24804,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="10"/>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="11"/>
       <c r="B121" s="3" t="s">
         <v>244</v>
       </c>
@@ -23653,8 +24813,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="10"/>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="11"/>
       <c r="B122" s="3" t="s">
         <v>246</v>
       </c>
@@ -23662,8 +24822,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="10"/>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="11"/>
       <c r="B123" s="3" t="s">
         <v>248</v>
       </c>
@@ -23671,8 +24831,8 @@
         <v>249</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="10"/>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="11"/>
       <c r="B124" s="3" t="s">
         <v>250</v>
       </c>
@@ -23680,8 +24840,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="10"/>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="11"/>
       <c r="B125" s="3" t="s">
         <v>252</v>
       </c>
@@ -23689,8 +24849,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="10"/>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="11"/>
       <c r="B126" s="3" t="s">
         <v>254</v>
       </c>
@@ -23698,8 +24858,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="10"/>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="11"/>
       <c r="B127" s="3" t="s">
         <v>256</v>
       </c>
@@ -23707,8 +24867,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="10"/>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="11"/>
       <c r="B128" s="3" t="s">
         <v>258</v>
       </c>
@@ -23716,8 +24876,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="10"/>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="11"/>
       <c r="B129" s="3" t="s">
         <v>260</v>
       </c>
@@ -23725,8 +24885,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="10"/>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="11"/>
       <c r="B130" s="3" t="s">
         <v>262</v>
       </c>
@@ -23734,8 +24894,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="10"/>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="11"/>
       <c r="B131" s="3" t="s">
         <v>264</v>
       </c>
@@ -23743,8 +24903,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="10"/>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="11"/>
       <c r="B132" s="3" t="s">
         <v>266</v>
       </c>
@@ -23752,8 +24912,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="10"/>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="11"/>
       <c r="B133" s="3" t="s">
         <v>268</v>
       </c>
@@ -23761,8 +24921,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="10"/>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="11"/>
       <c r="B134" s="3" t="s">
         <v>270</v>
       </c>
@@ -23770,8 +24930,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="10"/>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="11"/>
       <c r="B135" s="3" t="s">
         <v>272</v>
       </c>
@@ -23779,8 +24939,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="10"/>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="11"/>
       <c r="B136" s="3" t="s">
         <v>274</v>
       </c>
@@ -23788,8 +24948,8 @@
         <v>275</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="10"/>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="11"/>
       <c r="B137" s="3" t="s">
         <v>276</v>
       </c>
@@ -23797,8 +24957,8 @@
         <v>277</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="10"/>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="11"/>
       <c r="B138" s="3" t="s">
         <v>278</v>
       </c>
@@ -23806,8 +24966,8 @@
         <v>279</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="10"/>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="11"/>
       <c r="B139" s="3" t="s">
         <v>280</v>
       </c>
@@ -23815,8 +24975,8 @@
         <v>281</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="10"/>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="11"/>
       <c r="B140" s="3" t="s">
         <v>282</v>
       </c>
@@ -23824,8 +24984,8 @@
         <v>283</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="10"/>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="11"/>
       <c r="B141" s="3" t="s">
         <v>284</v>
       </c>
@@ -23833,8 +24993,8 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="10"/>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="11"/>
       <c r="B142" s="3" t="s">
         <v>286</v>
       </c>
@@ -23842,8 +25002,8 @@
         <v>287</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="10"/>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="11"/>
       <c r="B143" s="3" t="s">
         <v>288</v>
       </c>
@@ -23851,8 +25011,8 @@
         <v>289</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="10"/>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="11"/>
       <c r="B144" s="3" t="s">
         <v>290</v>
       </c>
@@ -23860,8 +25020,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="10"/>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="11"/>
       <c r="B145" s="3" t="s">
         <v>292</v>
       </c>
@@ -23869,8 +25029,8 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="10"/>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="11"/>
       <c r="B146" s="3" t="s">
         <v>294</v>
       </c>
@@ -23878,8 +25038,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="11"/>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="12"/>
       <c r="B147" s="5" t="s">
         <v>296</v>
       </c>
@@ -23887,8 +25047,8 @@
         <v>297</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="9" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="5" t="s">
@@ -23898,8 +25058,8 @@
         <v>298</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="12" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B149" s="3" t="s">
@@ -23909,8 +25069,8 @@
         <v>300</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="9"/>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="10"/>
       <c r="B150" s="5" t="s">
         <v>301</v>
       </c>
@@ -23918,8 +25078,8 @@
         <v>302</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="9" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B151" s="5" t="s">
@@ -23929,8 +25089,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="10" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="11" t="s">
         <v>305</v>
       </c>
       <c r="B152" s="3" t="s">
@@ -23940,8 +25100,8 @@
         <v>307</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="10"/>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="11"/>
       <c r="B153" s="3" t="s">
         <v>308</v>
       </c>
@@ -23949,8 +25109,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="10"/>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="11"/>
       <c r="B154" s="3" t="s">
         <v>310</v>
       </c>
@@ -23958,8 +25118,8 @@
         <v>311</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="10"/>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="11"/>
       <c r="B155" s="3" t="s">
         <v>312</v>
       </c>
@@ -23967,8 +25127,8 @@
         <v>313</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="10"/>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="11"/>
       <c r="B156" s="3" t="s">
         <v>314</v>
       </c>
@@ -23976,8 +25136,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="10"/>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="11"/>
       <c r="B157" s="3" t="s">
         <v>316</v>
       </c>
@@ -23985,8 +25145,8 @@
         <v>317</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="10"/>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="11"/>
       <c r="B158" s="3" t="s">
         <v>318</v>
       </c>
@@ -23994,8 +25154,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="10"/>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="11"/>
       <c r="B159" s="3" t="s">
         <v>320</v>
       </c>
@@ -24003,8 +25163,8 @@
         <v>321</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="10"/>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="11"/>
       <c r="B160" s="3" t="s">
         <v>322</v>
       </c>
@@ -24012,8 +25172,8 @@
         <v>323</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="10"/>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="11"/>
       <c r="B161" s="3" t="s">
         <v>324</v>
       </c>
@@ -24021,8 +25181,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="10"/>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="11"/>
       <c r="B162" s="3" t="s">
         <v>326</v>
       </c>
@@ -24030,8 +25190,8 @@
         <v>327</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="10"/>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="11"/>
       <c r="B163" s="3" t="s">
         <v>328</v>
       </c>
@@ -24039,8 +25199,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="10"/>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="11"/>
       <c r="B164" s="3" t="s">
         <v>330</v>
       </c>
@@ -24048,8 +25208,8 @@
         <v>331</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="10"/>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="11"/>
       <c r="B165" s="3" t="s">
         <v>332</v>
       </c>
@@ -24057,8 +25217,8 @@
         <v>333</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="10"/>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="11"/>
       <c r="B166" s="3" t="s">
         <v>334</v>
       </c>
@@ -24066,8 +25226,8 @@
         <v>335</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="10"/>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="11"/>
       <c r="B167" s="3" t="s">
         <v>336</v>
       </c>
@@ -24075,8 +25235,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="10"/>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="11"/>
       <c r="B168" s="3" t="s">
         <v>338</v>
       </c>
@@ -24084,8 +25244,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="10"/>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="11"/>
       <c r="B169" s="3" t="s">
         <v>340</v>
       </c>
@@ -24093,8 +25253,8 @@
         <v>341</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="10"/>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="11"/>
       <c r="B170" s="3" t="s">
         <v>342</v>
       </c>
@@ -24102,8 +25262,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="10"/>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="11"/>
       <c r="B171" s="3" t="s">
         <v>344</v>
       </c>
@@ -24111,8 +25271,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="10"/>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="11"/>
       <c r="B172" s="3" t="s">
         <v>346</v>
       </c>
@@ -24120,8 +25280,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="10"/>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="11"/>
       <c r="B173" s="3" t="s">
         <v>348</v>
       </c>
@@ -24129,8 +25289,8 @@
         <v>349</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="10"/>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="11"/>
       <c r="B174" s="3" t="s">
         <v>350</v>
       </c>
@@ -24138,8 +25298,8 @@
         <v>351</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="10"/>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="11"/>
       <c r="B175" s="3" t="s">
         <v>352</v>
       </c>
@@ -24147,8 +25307,8 @@
         <v>353</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="10"/>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="11"/>
       <c r="B176" s="3" t="s">
         <v>354</v>
       </c>
@@ -24156,8 +25316,8 @@
         <v>355</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="10"/>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="11"/>
       <c r="B177" s="3" t="s">
         <v>356</v>
       </c>
@@ -24165,8 +25325,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="11"/>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="12"/>
       <c r="B178" s="5" t="s">
         <v>358</v>
       </c>
@@ -24174,8 +25334,8 @@
         <v>359</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="9" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="5" t="s">
@@ -24185,8 +25345,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="10" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="11" t="s">
         <v>361</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -24196,8 +25356,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="10"/>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="11"/>
       <c r="B181" s="3" t="s">
         <v>364</v>
       </c>
@@ -24205,8 +25365,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="10"/>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="11"/>
       <c r="B182" s="3" t="s">
         <v>366</v>
       </c>
@@ -24214,8 +25374,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="10"/>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="11"/>
       <c r="B183" s="3" t="s">
         <v>368</v>
       </c>
@@ -24223,8 +25383,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="11"/>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="12"/>
       <c r="B184" s="5" t="s">
         <v>370</v>
       </c>
@@ -24232,8 +25392,8 @@
         <v>371</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="9" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B185" s="5" t="s">
@@ -24243,8 +25403,8 @@
         <v>373</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="9" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B186" s="5" t="s">
@@ -24254,8 +25414,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="10" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="11" t="s">
         <v>376</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -24265,8 +25425,8 @@
         <v>378</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="10"/>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="11"/>
       <c r="B188" s="3" t="s">
         <v>379</v>
       </c>
@@ -24274,8 +25434,8 @@
         <v>380</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="10"/>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="11"/>
       <c r="B189" s="3" t="s">
         <v>381</v>
       </c>
@@ -24283,8 +25443,8 @@
         <v>382</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="10"/>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="11"/>
       <c r="B190" s="3" t="s">
         <v>383</v>
       </c>
@@ -24292,8 +25452,8 @@
         <v>384</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="10"/>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="11"/>
       <c r="B191" s="3" t="s">
         <v>385</v>
       </c>
@@ -24301,8 +25461,8 @@
         <v>386</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="10"/>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="11"/>
       <c r="B192" s="3" t="s">
         <v>387</v>
       </c>
@@ -24310,8 +25470,8 @@
         <v>388</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="10"/>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="11"/>
       <c r="B193" s="3" t="s">
         <v>389</v>
       </c>
@@ -24319,8 +25479,8 @@
         <v>390</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="10"/>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="11"/>
       <c r="B194" s="3" t="s">
         <v>391</v>
       </c>
@@ -24328,8 +25488,8 @@
         <v>392</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="11"/>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="12"/>
       <c r="B195" s="5" t="s">
         <v>393</v>
       </c>
@@ -24337,8 +25497,8 @@
         <v>394</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="12" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B196" s="3" t="s">
@@ -24348,8 +25508,8 @@
         <v>396</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="12"/>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="9"/>
       <c r="B197" s="3" t="s">
         <v>397</v>
       </c>
@@ -24357,8 +25517,8 @@
         <v>398</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="12"/>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="9"/>
       <c r="B198" s="3" t="s">
         <v>399</v>
       </c>
@@ -24366,8 +25526,8 @@
         <v>400</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="9"/>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="10"/>
       <c r="B199" s="5" t="s">
         <v>401</v>
       </c>
@@ -24375,8 +25535,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="10" t="s">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="11" t="s">
         <v>403</v>
       </c>
       <c r="B200" s="3" t="s">
@@ -24386,8 +25546,8 @@
         <v>405</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="10"/>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="11"/>
       <c r="B201" s="3" t="s">
         <v>406</v>
       </c>
@@ -24395,8 +25555,8 @@
         <v>407</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="10"/>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="11"/>
       <c r="B202" s="3" t="s">
         <v>408</v>
       </c>
@@ -24404,8 +25564,8 @@
         <v>409</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="10"/>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="11"/>
       <c r="B203" s="3" t="s">
         <v>410</v>
       </c>
@@ -24413,8 +25573,8 @@
         <v>411</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="10"/>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="11"/>
       <c r="B204" s="3" t="s">
         <v>412</v>
       </c>
@@ -24422,8 +25582,8 @@
         <v>413</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="10"/>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="11"/>
       <c r="B205" s="3" t="s">
         <v>414</v>
       </c>
@@ -24431,8 +25591,8 @@
         <v>415</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="10"/>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="11"/>
       <c r="B206" s="3" t="s">
         <v>416</v>
       </c>
@@ -24440,8 +25600,8 @@
         <v>417</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="10"/>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="11"/>
       <c r="B207" s="3" t="s">
         <v>418</v>
       </c>
@@ -24449,8 +25609,8 @@
         <v>419</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="10"/>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="11"/>
       <c r="B208" s="3" t="s">
         <v>420</v>
       </c>
@@ -24458,8 +25618,8 @@
         <v>421</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="10"/>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="11"/>
       <c r="B209" s="3" t="s">
         <v>422</v>
       </c>
@@ -24467,8 +25627,8 @@
         <v>423</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="11"/>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="12"/>
       <c r="B210" s="5" t="s">
         <v>424</v>
       </c>
@@ -24476,8 +25636,8 @@
         <v>425</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="9" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="10" t="s">
         <v>77</v>
       </c>
       <c r="B211" s="5" t="s">
@@ -24487,8 +25647,8 @@
         <v>427</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="10" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="11" t="s">
         <v>428</v>
       </c>
       <c r="B212" s="3" t="s">
@@ -24498,8 +25658,8 @@
         <v>430</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="10"/>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="11"/>
       <c r="B213" s="3" t="s">
         <v>431</v>
       </c>
@@ -24507,8 +25667,8 @@
         <v>432</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="10"/>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="11"/>
       <c r="B214" s="3" t="s">
         <v>433</v>
       </c>
@@ -24516,8 +25676,8 @@
         <v>434</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="10"/>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="11"/>
       <c r="B215" s="3" t="s">
         <v>435</v>
       </c>
@@ -24525,8 +25685,8 @@
         <v>436</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="11"/>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="12"/>
       <c r="B216" s="5" t="s">
         <v>437</v>
       </c>
@@ -24537,6 +25697,21 @@
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="24">
+    <mergeCell ref="A1"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A17:C18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A40"/>
+    <mergeCell ref="A41:A55"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="A57"/>
+    <mergeCell ref="A58:A69"/>
+    <mergeCell ref="A70"/>
+    <mergeCell ref="A71:A147"/>
+    <mergeCell ref="A148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A151"/>
+    <mergeCell ref="A152:A178"/>
     <mergeCell ref="A196:A199"/>
     <mergeCell ref="A200:A210"/>
     <mergeCell ref="A211"/>
@@ -24546,21 +25721,6 @@
     <mergeCell ref="A185"/>
     <mergeCell ref="A186"/>
     <mergeCell ref="A187:A195"/>
-    <mergeCell ref="A71:A147"/>
-    <mergeCell ref="A148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A151"/>
-    <mergeCell ref="A152:A178"/>
-    <mergeCell ref="A41:A55"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="A57"/>
-    <mergeCell ref="A58:A69"/>
-    <mergeCell ref="A70"/>
-    <mergeCell ref="A1"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="A17:C18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24569,7 +25729,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:AN10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -24579,7 +25739,7 @@
     <col min="8" max="40" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -24701,7 +25861,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -24823,7 +25983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -24945,7 +26105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -25067,7 +26227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -25189,7 +26349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -25311,7 +26471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -25433,7 +26593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -25555,7 +26715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -25677,7 +26837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -25808,7 +26968,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -25817,7 +26977,7 @@
     <col min="5" max="7" width="8" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -25840,7 +27000,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -25863,7 +27023,7 @@
         <v>2.9779280000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -25886,7 +27046,7 @@
         <v>2.3407620000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -25909,7 +27069,7 @@
         <v>4.71405E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -25932,7 +27092,7 @@
         <v>2.7144160000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -25955,7 +27115,7 @@
         <v>1.3123350000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -25978,7 +27138,7 @@
         <v>2.8674419999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -26001,7 +27161,7 @@
         <v>4.6135370000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -26024,7 +27184,7 @@
         <v>3.0607280000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -26056,7 +27216,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:V10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -26067,7 +27227,7 @@
     <col min="11" max="22" width="8" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -26135,7 +27295,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -26203,7 +27363,7 @@
         <v>2.8087170000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -26271,7 +27431,7 @@
         <v>0.11991895</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -26339,7 +27499,7 @@
         <v>2.422407E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -26407,7 +27567,7 @@
         <v>5.3670809999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -26475,7 +27635,7 @@
         <v>5.684409E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -26543,7 +27703,7 @@
         <v>7.8457349999999995E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -26611,7 +27771,7 @@
         <v>6.06676E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -26679,7 +27839,7 @@
         <v>5.475323E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -26756,7 +27916,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BT10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -26790,7 +27950,7 @@
     <col min="70" max="72" width="8" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -27008,7 +28168,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -27223,7 +28383,7 @@
         <v>8.1738909999999998E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -27438,7 +28598,7 @@
         <v>0.14090235000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -27653,7 +28813,7 @@
         <v>0.25681408</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -27868,7 +29028,7 @@
         <v>7.0735229999999996E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -28083,7 +29243,7 @@
         <v>5.188127E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -28298,7 +29458,7 @@
         <v>0.13777246000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -28513,7 +29673,7 @@
         <v>2.6523049999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -28728,7 +29888,7 @@
         <v>5.5876849999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -28952,7 +30112,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AZ10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -28962,7 +30122,7 @@
     <col min="8" max="52" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -29120,7 +30280,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -29278,7 +30438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -29436,7 +30596,7 @@
         <v>1.105542E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -29594,7 +30754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -29752,7 +30912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -29910,7 +31070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -30068,7 +31228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -30226,7 +31386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -30384,7 +31544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -30551,7 +31711,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -30560,7 +31720,7 @@
     <col min="5" max="7" width="8" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -30583,7 +31743,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -30606,7 +31766,7 @@
         <v>3.9015670000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -30629,7 +31789,7 @@
         <v>4.7382899999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -30652,7 +31812,7 @@
         <v>0.20993385000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -30675,7 +31835,7 @@
         <v>4.3724199999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -30698,7 +31858,7 @@
         <v>1.6749790000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -30721,7 +31881,7 @@
         <v>0.11915501000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -30744,7 +31904,7 @@
         <v>3.738872E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -30767,7 +31927,7 @@
         <v>0.10019425999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -30799,7 +31959,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -30808,7 +31968,7 @@
     <col min="5" max="7" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -30831,7 +31991,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -30854,7 +32014,7 @@
         <v>2.422407E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -30877,7 +32037,7 @@
         <v>2.3273729999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -30900,7 +32060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -30923,7 +32083,7 @@
         <v>1.9238990000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -30946,7 +32106,7 @@
         <v>7.3124699999999997E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -30969,7 +32129,7 @@
         <v>7.6376300000000003E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -30992,7 +32152,7 @@
         <v>8.9752700000000005E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -31015,7 +32175,7 @@
         <v>1.017213E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -31047,7 +32207,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AQ10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -31058,7 +32218,7 @@
     <col min="17" max="43" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -31189,7 +32349,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -31320,7 +32480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -31451,7 +32611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -31582,7 +32742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -31713,7 +32873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -31844,7 +33004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -31975,7 +33135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -32106,7 +33266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -32237,7 +33397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -32377,7 +33537,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AQ10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -32389,7 +33549,7 @@
     <col min="17" max="43" width="12" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -32520,7 +33680,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -32651,7 +33811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -32782,7 +33942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -32913,7 +34073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -33044,7 +34204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -33175,7 +34335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -33306,7 +34466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -33437,7 +34597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -33568,7 +34728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -33708,7 +34868,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:ID10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -33719,7 +34879,7 @@
     <col min="11" max="238" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -34435,7 +35595,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="2" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -34458,13 +35618,13 @@
         <v>2.8674419999999999E-2</v>
       </c>
       <c r="H2" s="8">
-        <v>1.6666700000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="8">
         <v>0</v>
       </c>
       <c r="J2" s="8">
-        <v>3.7267799999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="8">
         <v>0</v>
@@ -35151,7 +36311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -35201,13 +36361,13 @@
         <v>0</v>
       </c>
       <c r="Q3" s="8">
-        <v>2.833333E-2</v>
+        <v>2.666667E-2</v>
       </c>
       <c r="R3" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S3" s="8">
-        <v>5.0470010000000003E-2</v>
+        <v>4.6785559999999997E-2</v>
       </c>
       <c r="T3" s="8">
         <v>0</v>
@@ -35867,7 +37027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -36583,7 +37743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -37299,7 +38459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -38015,7 +39175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -38038,13 +39198,13 @@
         <v>2.0816660000000001E-2</v>
       </c>
       <c r="H7" s="8">
-        <v>8.3332999999999996E-4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="8">
         <v>0</v>
       </c>
       <c r="J7" s="8">
-        <v>1.8633899999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="8">
         <v>0</v>
@@ -38731,7 +39891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -39447,7 +40607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -40163,7 +41323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:238" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:238" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
